--- a/Tools/Config/Datas/BuffSetting.xlsx
+++ b/Tools/Config/Datas/BuffSetting.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ACTGameEditor\Tools\Config\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="18350" windowHeight="6880"/>
   </bookViews>
   <sheets>
-    <sheet name="Buff" sheetId="4" r:id="rId1"/>
-    <sheet name="EffectModify" sheetId="5" r:id="rId2"/>
-    <sheet name="FormulaType" sheetId="6" r:id="rId3"/>
+    <sheet name="Buff" sheetId="1" r:id="rId1"/>
+    <sheet name="EffectModify" sheetId="2" r:id="rId2"/>
+    <sheet name="FormulaType" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,20 +43,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 从20000开始
 每种大类型间隔100
 未来不够后续拓展</t>
@@ -62,20 +58,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 0为不能叠加
 1为能叠加</t>
         </r>
@@ -85,20 +72,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 0为不处理
 1为刷新时间（必须要有固定时间配置）
 2为叠加时间
@@ -111,20 +89,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 一个buff只能配置一个控制类修饰器，多个只会生效第一个，为了提高运行效率！！！</t>
         </r>
       </text>
@@ -133,20 +102,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>admin:
 -1代表无限时长</t>
         </r>
       </text>
@@ -156,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="148">
   <si>
     <t>##var</t>
   </si>
@@ -393,6 +353,48 @@
   </si>
   <si>
     <t>PostReceiveDamage</t>
+  </si>
+  <si>
+    <t>攻击后加攻-触发器</t>
+  </si>
+  <si>
+    <t>TriggerBuff</t>
+  </si>
+  <si>
+    <t>普攻或大招主轴结束后给自己挂 5 秒加攻；被动伤害不会走施法点</t>
+  </si>
+  <si>
+    <t>PostSpell</t>
+  </si>
+  <si>
+    <t>#IsNormalOrUltimateSpell</t>
+  </si>
+  <si>
+    <t>攻击力提升20%</t>
+  </si>
+  <si>
+    <t>攻击力提升 20%，持续 5 秒，重复获得时刷新时间</t>
+  </si>
+  <si>
+    <t>命中点燃-触发器</t>
+  </si>
+  <si>
+    <t>主动技能真实命中后给敌方挂点燃；Buff 伤害不会触发</t>
+  </si>
+  <si>
+    <t>PostCauseDamage</t>
+  </si>
+  <si>
+    <t>#IsActiveSkillHit</t>
+  </si>
+  <si>
+    <t>点燃</t>
+  </si>
+  <si>
+    <t>Buff.Fire.Ignite</t>
+  </si>
+  <si>
+    <t>每秒造成 50 点火属性伤害，持续 5 秒，重复施加刷新时间</t>
   </si>
   <si>
     <t>EffectModifyID</t>
@@ -570,7 +572,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -730,13 +732,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1083,167 +1079,164 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="23" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1272,13 +1265,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="22" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1333,11 +1319,6 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="00C6EFCE"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1604,19 +1585,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="19.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="28.25" style="11" customWidth="1"/>
+    <col min="3" max="3" width="24.5833333333333" customWidth="1"/>
+    <col min="4" max="4" width="28.25" style="8" customWidth="1"/>
     <col min="5" max="5" width="16.75" customWidth="1"/>
     <col min="6" max="6" width="17.25" customWidth="1"/>
-    <col min="7" max="8" width="26.75" customWidth="1"/>
+    <col min="7" max="7" width="26.75" customWidth="1"/>
+    <col min="8" max="8" width="31.75" customWidth="1"/>
     <col min="9" max="9" width="15.75" customWidth="1"/>
     <col min="10" max="10" width="12.3333333333333" customWidth="1"/>
     <col min="11" max="11" width="10.75" customWidth="1"/>
     <col min="12" max="12" width="16.0833333333333" customWidth="1"/>
-    <col min="13" max="13" width="23.25" style="12" customWidth="1"/>
+    <col min="13" max="13" width="23.25" style="9" customWidth="1"/>
     <col min="14" max="14" width="15.9166666666667" customWidth="1"/>
     <col min="15" max="17" width="18.6666666666667" customWidth="1"/>
     <col min="18" max="18" width="14.5" customWidth="1"/>
@@ -1633,10 +1615,10 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1663,34 +1645,34 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="17" t="s">
+      <c r="P1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="17" t="s">
+      <c r="Q1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="17" t="s">
+      <c r="S1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="17" t="s">
+      <c r="T1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="17" t="s">
+      <c r="U1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="18" t="s">
+      <c r="V1" s="15" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1700,37 +1682,37 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="20"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="17"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="11" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -1757,34 +1739,34 @@
       <c r="L3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="T3" s="17" t="s">
+      <c r="T3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="U3" s="17" t="s">
+      <c r="U3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="V3" s="18" t="s">
+      <c r="V3" s="15" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1795,10 +1777,10 @@
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="11" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -1825,484 +1807,655 @@
       <c r="L4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="N4" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="16" t="s">
+      <c r="O4" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="17" t="s">
+      <c r="P4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="17" t="s">
+      <c r="Q4" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="R4" s="17" t="s">
+      <c r="R4" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="17" t="s">
+      <c r="S4" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="T4" s="17" t="s">
+      <c r="T4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="U4" s="17" t="s">
+      <c r="U4" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="V4" s="18" t="s">
+      <c r="V4" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" s="7" customFormat="1" spans="1:22">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:22">
+      <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="23"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="7" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="N5" t="s">
         <v>49</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" t="s">
         <v>50</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="R5" t="s">
         <v>49</v>
       </c>
-      <c r="S5" s="7" t="s">
+      <c r="S5" t="s">
         <v>49</v>
       </c>
-      <c r="T5" s="7" t="s">
+      <c r="T5" t="s">
         <v>49</v>
       </c>
-      <c r="U5" s="7" t="s">
+      <c r="U5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6" s="7" customFormat="1" spans="1:22">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:22">
+      <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="23"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="M6" s="24"/>
-      <c r="U6" s="7" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="U6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" s="7" customFormat="1" spans="1:22">
-      <c r="B7" s="10">
+    <row r="7" spans="1:22">
+      <c r="B7" s="7">
         <v>20001</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="10">
-        <v>0</v>
-      </c>
-      <c r="J7" s="10">
-        <v>0</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7">
+      <c r="I7" s="7">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>3</v>
       </c>
-      <c r="M7" s="24">
-        <v>1</v>
-      </c>
-      <c r="N7" s="7">
-        <v>1</v>
-      </c>
-      <c r="P7" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" s="7" customFormat="1" spans="1:22">
-      <c r="B8" s="10">
+      <c r="M7" s="9">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="B8" s="7">
         <v>20101</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8">
         <v>2</v>
       </c>
-      <c r="F8" s="7">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="10">
-        <v>0</v>
-      </c>
-      <c r="J8" s="10">
-        <v>0</v>
-      </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7">
+      <c r="I8" s="7">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="24">
+      <c r="M8" s="9">
         <v>2</v>
       </c>
-      <c r="N8" s="7">
-        <v>1</v>
-      </c>
-      <c r="P8" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" s="7" customFormat="1" spans="1:22">
-      <c r="B9" s="10">
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="B9" s="7">
         <v>20201</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9">
         <v>3</v>
       </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="10">
-        <v>0</v>
-      </c>
-      <c r="J9" s="10">
-        <v>0</v>
-      </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7">
+      <c r="I9" s="7">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>3</v>
       </c>
-      <c r="M9" s="24">
+      <c r="M9" s="9">
         <v>3</v>
       </c>
-      <c r="N9" s="7">
-        <v>1</v>
-      </c>
-      <c r="P9" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" s="7" customFormat="1" spans="1:22">
-      <c r="B10" s="10">
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="B10" s="7">
         <v>20301</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10">
         <v>4</v>
       </c>
-      <c r="F10" s="7">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="10">
-        <v>0</v>
-      </c>
-      <c r="J10" s="10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7">
-        <v>1</v>
-      </c>
-      <c r="M10" s="24">
+      <c r="I10" s="7">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10" s="9">
         <v>4</v>
       </c>
-      <c r="N10" s="7">
+      <c r="N10">
         <v>5</v>
       </c>
-      <c r="T10" s="7">
+      <c r="T10">
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" s="7" customFormat="1" spans="1:22">
-      <c r="B11" s="10">
+    <row r="11" spans="1:22">
+      <c r="B11" s="7">
         <v>20302</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11">
         <v>4</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="10">
-        <v>0</v>
-      </c>
-      <c r="J11" s="10">
-        <v>0</v>
-      </c>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7">
-        <v>1</v>
-      </c>
-      <c r="M11" s="24">
+      <c r="I11" s="7">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11" s="9">
         <v>4</v>
       </c>
-      <c r="N11" s="7">
+      <c r="N11">
         <v>6</v>
       </c>
-      <c r="T11" s="7">
+      <c r="T11">
         <v>0.5</v>
       </c>
-      <c r="U11" s="7" t="s">
+      <c r="U11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12" s="7" customFormat="1" spans="1:22">
-      <c r="B12" s="10">
+    <row r="12" spans="1:22">
+      <c r="B12" s="7">
         <v>20401</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12">
         <v>5</v>
       </c>
-      <c r="F12" s="7">
-        <v>1</v>
-      </c>
-      <c r="I12" s="10">
-        <v>0</v>
-      </c>
-      <c r="J12" s="10">
-        <v>1</v>
-      </c>
-      <c r="K12" s="7">
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7">
+        <v>0</v>
+      </c>
+      <c r="J12" s="7">
+        <v>1</v>
+      </c>
+      <c r="K12">
         <v>10</v>
       </c>
-      <c r="L12" s="7">
-        <v>1</v>
-      </c>
-      <c r="M12" s="24">
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12" s="9">
         <v>6</v>
       </c>
-      <c r="N12" s="7">
+      <c r="N12">
         <v>2</v>
       </c>
-      <c r="T12" s="7">
+      <c r="T12">
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" s="7" customFormat="1" spans="1:22">
-      <c r="B13" s="10">
+    <row r="13" spans="1:22">
+      <c r="B13" s="7">
         <v>20410</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13">
         <v>5</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13">
         <v>10</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" t="s">
         <v>67</v>
       </c>
-      <c r="I13" s="10">
-        <v>1</v>
-      </c>
-      <c r="J13" s="10">
-        <v>0</v>
-      </c>
-      <c r="L13" s="7">
-        <v>1</v>
-      </c>
-      <c r="M13" s="24" t="s">
+      <c r="I13" s="7">
+        <v>1</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="N13" s="7">
+      <c r="N13">
         <v>5</v>
       </c>
-      <c r="T13" s="7">
+      <c r="T13">
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" s="10" customFormat="1" spans="1:22">
-      <c r="B14" s="10">
+    <row r="14" s="7" customFormat="1" spans="1:22">
+      <c r="B14" s="7">
         <v>20501</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14">
         <v>10</v>
       </c>
-      <c r="F14" s="7">
-        <v>1</v>
-      </c>
-      <c r="I14" s="10">
-        <v>1</v>
-      </c>
-      <c r="J14" s="10">
-        <v>0</v>
-      </c>
-      <c r="L14" s="7">
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="7">
+        <v>1</v>
+      </c>
+      <c r="J14" s="7">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>2</v>
       </c>
-      <c r="M14" s="24">
+      <c r="M14" s="9">
         <v>7</v>
       </c>
-      <c r="N14" s="7">
+      <c r="N14">
         <v>2</v>
       </c>
-      <c r="T14" s="7">
+      <c r="T14">
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" s="7" customFormat="1" spans="1:22">
-      <c r="B15" s="10">
+    <row r="15" spans="1:22">
+      <c r="B15" s="7">
         <v>30001</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15">
         <v>15</v>
       </c>
-      <c r="F15" s="7">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7" t="s">
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="10">
-        <v>1</v>
-      </c>
-      <c r="J15" s="10">
-        <v>0</v>
-      </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7">
-        <v>0</v>
-      </c>
-      <c r="M15" s="24">
+      <c r="I15" s="7">
+        <v>1</v>
+      </c>
+      <c r="J15" s="7">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9">
         <v>8</v>
       </c>
-      <c r="O15" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="7" t="s">
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="s">
         <v>73</v>
       </c>
-      <c r="R15" s="7">
+      <c r="R15">
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" s="7" customFormat="1" spans="1:22">
-      <c r="B16" s="10">
+    <row r="16" spans="1:22">
+      <c r="B16" s="7">
         <v>30002</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16">
         <v>20</v>
       </c>
-      <c r="F16" s="7">
-        <v>1</v>
-      </c>
-      <c r="H16" s="7" t="s">
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
         <v>76</v>
       </c>
-      <c r="I16" s="10">
-        <v>1</v>
-      </c>
-      <c r="J16" s="10">
-        <v>0</v>
-      </c>
-      <c r="L16" s="7">
-        <v>0</v>
-      </c>
-      <c r="M16" s="24" t="s">
+      <c r="I16" s="7">
+        <v>1</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="N16" s="7">
+      <c r="N16">
         <v>-1</v>
       </c>
-      <c r="P16" s="7">
-        <v>1</v>
-      </c>
-      <c r="V16" s="7" t="s">
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="V16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" s="7" customFormat="1" spans="4:13">
-      <c r="D17" s="23"/>
-      <c r="M17" s="24"/>
-    </row>
-    <row r="18" s="7" customFormat="1" spans="4:13">
-      <c r="D18" s="23"/>
-      <c r="M18" s="24"/>
+    <row r="17" spans="2:21">
+      <c r="B17">
+        <v>31000</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17">
+        <v>21</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>81</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>4</v>
+      </c>
+      <c r="M17" s="9">
+        <v>20</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>82</v>
+      </c>
+      <c r="U17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21">
+      <c r="B18">
+        <v>31001</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18">
+        <v>21</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="H18" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18" s="9">
+        <v>21</v>
+      </c>
+      <c r="N18">
+        <v>5</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21">
+      <c r="B19">
+        <v>31010</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19">
+        <v>22</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>4</v>
+      </c>
+      <c r="M19">
+        <v>23</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>88</v>
+      </c>
+      <c r="U19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21">
+      <c r="B20">
+        <v>31011</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>22</v>
+      </c>
+      <c r="N20">
+        <v>5</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2312,9 +2465,6 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="M16" numberStoredAsText="1"/>
-  </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -2322,7 +2472,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="26" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="17.9166666666667" customWidth="1"/>
@@ -2340,52 +2490,52 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
     </row>
     <row r="3" customHeight="1" spans="1:9">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>23</v>
@@ -2411,186 +2561,175 @@
         <v>28</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A5" s="3" t="s">
+    <row r="5" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6" t="s">
-        <v>95</v>
+      <c r="C5" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>96</v>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>110</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:9">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>96</v>
+      <c r="C7" t="s">
+        <v>110</v>
       </c>
       <c r="I7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A8" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>102</v>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:9">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>3</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9">
         <v>1001</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="5">
         <v>2</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7">
+      <c r="G9">
         <v>30</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A10" s="3" t="s">
+    </row>
+    <row r="10" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="I10" s="6"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="11" customHeight="1" spans="1:9">
-      <c r="A11" s="7"/>
       <c r="B11">
         <v>8</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="7">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7">
-        <v>1</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A12" s="3" t="s">
+      <c r="C11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="I12" s="6"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="13" customHeight="1" spans="1:9">
       <c r="B13">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -2605,75 +2744,73 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A14" s="3" t="s">
+    <row r="14" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I14" s="6"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
       <c r="B15">
         <v>10</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>118</v>
+      <c r="C15" t="s">
+        <v>132</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15">
         <v>1007</v>
       </c>
       <c r="G15">
         <v>20</v>
       </c>
     </row>
-    <row r="16" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A16" s="3" t="s">
+    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I16" s="6"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="17" customHeight="1" spans="1:9">
       <c r="B17">
         <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -2685,23 +2822,23 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A18" s="3" t="s">
+    <row r="18" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6" t="s">
-        <v>122</v>
+      <c r="B18" s="4"/>
+      <c r="C18" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -2709,25 +2846,24 @@
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A20" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6" t="s">
-        <v>122</v>
+      <c r="B20" s="4"/>
+      <c r="C20" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="I20" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
@@ -2735,7 +2871,66 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:9">
+      <c r="B22">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22">
+        <v>31001</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:9">
+      <c r="B23">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23">
+        <v>1001</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:9">
+      <c r="B24">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:9">
+      <c r="B25">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25">
+        <v>31011</v>
       </c>
     </row>
   </sheetData>
@@ -2763,29 +2958,29 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -2806,16 +3001,16 @@
         <v>28</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:5">

--- a/Tools/Config/Datas/BuffSetting.xlsx
+++ b/Tools/Config/Datas/BuffSetting.xlsx
@@ -670,7 +670,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="22"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -712,6 +712,7 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1144,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
     <col width="24.5833333333333" customWidth="1" min="3" max="3"/>
@@ -2330,6 +2331,299 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>20601</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>冻结</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TimeBuff</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Buff.Freeze|Buff.Debuff</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>停动画与位移（实体钟=0），点燃跳伤仍走世界钟</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>24</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>20602</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>长冻结</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TimeBuff</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Buff.Freeze|Buff.Debuff</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>8 秒冻结，方便看冰壳；点燃/霜蚀仍走世界钟</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>24</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>20701</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>霜蚀</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TimeBuff</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Buff.Debuff</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>每秒 40 点冰伤，持续 6 秒。冻结中应继续跳（世界钟）</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>20801</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>测试护盾</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TimeBuff</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Buff.Buff</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>吸收 400 点伤害，持续 10 秒。可与冻结叠测</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>26</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>21001</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>对冻结增伤</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TimeBuff</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>16</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Buff.Buff</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>挂在攻击者：打带 Buff.Freeze 的目标最终伤害 +50%，持续 15 秒</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>27</v>
+      </c>
+      <c r="N25" t="n">
+        <v>15</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="I5:J13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
@@ -2347,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.66666666666667" defaultRowHeight="26" customHeight="1"/>
   <cols>
     <col width="17.9166666666667" customWidth="1" min="2" max="2"/>
@@ -2974,6 +3268,355 @@
       </c>
       <c r="D25" t="n">
         <v>31011</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>灼烧跳伤（补齐 Id=4，给 20301/20302/20410）</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>DamageCalcuFormulaType</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>DamageType</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>CanCrit</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>固定值</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BuffHpDamage</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>中毒跳伤（补齐 Id=6，给 20401/20410）</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>DamageCalcuFormulaType</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>DamageType</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>CanCrit</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>固定值</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BuffHpDamage</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>持续治疗（补齐 Id=7，给 20501）</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>ResourceFormulaType</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>AttributeType</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BuffResource</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G31" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>冻结控制</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>控制标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>24</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PlayerControll</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Buff.MoveForbid|Buff.SkillForbid|Buff.Freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>霜蚀跳伤</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>DamageCalcuFormulaType</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>DamageType</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>CanCrit</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>固定值</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>25</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BuffHpDamage</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>护盾吸收</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>单层盾量</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>26</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AddShield</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>对冻结目标增伤</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>FilterType=5 目标Tag</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>ApplySide</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>百分点</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>目标 Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>27</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ActionModify</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>50</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Buff.Freeze</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Tools/Config/Datas/BuffSetting.xlsx
+++ b/Tools/Config/Datas/BuffSetting.xlsx
@@ -1653,7 +1653,7 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2386,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -2444,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
